--- a/AAII_Financials/Quarterly/COE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
   <si>
     <t>COE</t>
   </si>
@@ -656,390 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="I7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="K7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="M7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="O7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="W7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F8" s="3">
+        <v>7500</v>
+      </c>
+      <c r="G8" s="3">
+        <v>7800</v>
+      </c>
+      <c r="H8" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I8" s="3">
         <v>5600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="J8" s="3">
         <v>5100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="K8" s="3">
         <v>4600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="L8" s="3">
         <v>3500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="M8" s="3">
         <v>1900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="N8" s="3">
         <v>2181500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="O8" s="3">
         <v>573600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="P8" s="3">
         <v>579800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="Q8" s="3">
         <v>92400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="R8" s="3">
         <v>535100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="S8" s="3">
         <v>538500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="T8" s="3">
         <v>72700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="U8" s="3">
         <v>76800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="V8" s="3">
         <v>62000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="W8" s="3">
         <v>62900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="X8" s="3">
         <v>53900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="Y8" s="3">
         <v>48700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="Z8" s="3">
         <v>43300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="AA8" s="3">
         <v>44000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="AB8" s="3">
         <v>39400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AC8" s="3">
         <v>37700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AD8" s="3">
         <v>38700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AE8" s="3">
         <v>35000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AF8" s="3">
         <v>28500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AG8" s="3">
         <v>23200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AH8" s="3">
         <v>18600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AI8" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I9" s="3">
         <v>1200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="J9" s="3">
         <v>1100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="K9" s="3">
         <v>1000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="L9" s="3">
         <v>700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="N9" s="3">
         <v>558000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="O9" s="3">
         <v>151900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="P9" s="3">
         <v>158100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="Q9" s="3">
         <v>24600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="R9" s="3">
         <v>146100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="S9" s="3">
         <v>146700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="T9" s="3">
         <v>21200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="U9" s="3">
         <v>22700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="V9" s="3">
         <v>17500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="W9" s="3">
         <v>17900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="X9" s="3">
         <v>16400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="Y9" s="3">
         <v>16100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="Z9" s="3">
         <v>16200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="AA9" s="3">
         <v>15900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="AB9" s="3">
         <v>13500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="AC9" s="3">
         <v>13300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AD9" s="3">
         <v>14500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AE9" s="3">
         <v>13400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AF9" s="3">
         <v>10600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AG9" s="3">
         <v>8000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AH9" s="3">
         <v>6600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AI9" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4400</v>
+        <v>8600</v>
       </c>
       <c r="E10" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>6000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J10" s="3">
         <v>4000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="K10" s="3">
         <v>3600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="L10" s="3">
         <v>2800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="M10" s="3">
         <v>1500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="N10" s="3">
         <v>1623500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="O10" s="3">
         <v>421700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="P10" s="3">
         <v>421700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="Q10" s="3">
         <v>67800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="R10" s="3">
         <v>389000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="S10" s="3">
         <v>391800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="T10" s="3">
         <v>51600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="U10" s="3">
         <v>54100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="V10" s="3">
         <v>44500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="W10" s="3">
         <v>45100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="X10" s="3">
         <v>37400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="Y10" s="3">
         <v>32600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="Z10" s="3">
         <v>27100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="AA10" s="3">
         <v>28100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="AB10" s="3">
         <v>25900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AC10" s="3">
         <v>24300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AD10" s="3">
         <v>24100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AE10" s="3">
         <v>21700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AF10" s="3">
         <v>17900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AG10" s="3">
         <v>15200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AH10" s="3">
         <v>12000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AI10" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,94 +1134,114 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>900</v>
+      </c>
+      <c r="F12" s="3">
+        <v>900</v>
+      </c>
+      <c r="G12" s="3">
+        <v>900</v>
+      </c>
+      <c r="H12" s="3">
+        <v>700</v>
+      </c>
+      <c r="I12" s="3">
         <v>400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="J12" s="3">
         <v>400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="K12" s="3">
         <v>600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="M12" s="3">
         <v>1100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="N12" s="3">
         <v>178800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="O12" s="3">
         <v>40700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="P12" s="3">
         <v>65000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="Q12" s="3">
         <v>8900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="R12" s="3">
         <v>44600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="S12" s="3">
         <v>43800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="T12" s="3">
         <v>5700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="U12" s="3">
         <v>5700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="V12" s="3">
         <v>5800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="W12" s="3">
         <v>5900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="X12" s="3">
         <v>6300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="Y12" s="3">
         <v>6200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="Z12" s="3">
         <v>6200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="AA12" s="3">
         <v>6600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="AB12" s="3">
         <v>6200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="AC12" s="3">
         <v>7500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AD12" s="3">
         <v>9000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AE12" s="3">
         <v>9100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AF12" s="3">
         <v>7500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AG12" s="3">
         <v>7400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AH12" s="3">
         <v>6700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AI12" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1242,8 +1326,23 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1259,77 +1358,92 @@
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>21500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="O14" s="3">
         <v>31800</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-7400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="S14" s="3">
         <v>-7600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="T14" s="3">
         <v>-1000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="U14" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1100</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1414,8 +1528,23 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1572,215 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F17" s="3">
+        <v>11800</v>
+      </c>
+      <c r="G17" s="3">
+        <v>11700</v>
+      </c>
+      <c r="H17" s="3">
+        <v>9200</v>
+      </c>
+      <c r="I17" s="3">
         <v>7900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="J17" s="3">
         <v>7200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="K17" s="3">
         <v>7200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="L17" s="3">
         <v>7600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="M17" s="3">
         <v>5400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="N17" s="3">
         <v>2132200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="O17" s="3">
         <v>515200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="P17" s="3">
         <v>613600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="Q17" s="3">
         <v>91500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="R17" s="3">
         <v>524100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="S17" s="3">
         <v>517100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="T17" s="3">
         <v>68700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="U17" s="3">
         <v>69800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="V17" s="3">
         <v>63000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="W17" s="3">
         <v>64000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="X17" s="3">
         <v>59200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="Y17" s="3">
         <v>58400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Z17" s="3">
         <v>63100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="AA17" s="3">
         <v>56900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="AB17" s="3">
         <v>50100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AC17" s="3">
         <v>53500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AD17" s="3">
         <v>61400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AE17" s="3">
         <v>55800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AF17" s="3">
         <v>48900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AG17" s="3">
         <v>43600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AH17" s="3">
         <v>40600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AI17" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-2300</v>
+        <v>-2400</v>
       </c>
       <c r="E18" s="3">
-        <v>-2100</v>
+        <v>-3900</v>
       </c>
       <c r="F18" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="L18" s="3">
         <v>-4100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="M18" s="3">
         <v>-3500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="N18" s="3">
         <v>49300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="O18" s="3">
         <v>58400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="P18" s="3">
         <v>-33800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="Q18" s="3">
         <v>900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="R18" s="3">
         <v>11000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="S18" s="3">
         <v>21400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="T18" s="3">
         <v>4000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="U18" s="3">
         <v>7100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="V18" s="3">
         <v>-1000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="W18" s="3">
         <v>-1000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="X18" s="3">
         <v>-5400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="Y18" s="3">
         <v>-9700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="Z18" s="3">
         <v>-19800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="AA18" s="3">
         <v>-12900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="AB18" s="3">
         <v>-10700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AC18" s="3">
         <v>-15900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AD18" s="3">
         <v>-22700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AE18" s="3">
         <v>-20700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AF18" s="3">
         <v>-20400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AG18" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AH18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AI18" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1647,117 +1811,137 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="J20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="N20" s="3">
         <v>25100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="O20" s="3">
         <v>-6200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="P20" s="3">
         <v>9600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="Q20" s="3">
         <v>1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="R20" s="3">
         <v>11900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="S20" s="3">
         <v>11700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="T20" s="3">
         <v>1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="U20" s="3">
         <v>1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="Z20" s="3">
         <v>-400</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="W20" s="3">
-        <v>500</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-800</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-200</v>
       </c>
       <c r="AA20" s="3">
         <v>-100</v>
       </c>
       <c r="AB20" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AH20" s="3">
         <v>-400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AI20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>16</v>
+      <c r="D21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-2000</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>16</v>
@@ -1819,8 +2003,23 @@
       <c r="AD21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1836,8 +2035,8 @@
       <c r="G22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>16</v>
@@ -1848,29 +2047,29 @@
       <c r="K22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>16</v>
+      <c r="L22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1905,94 +2104,124 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-2400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="J23" s="3">
         <v>-2000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="K23" s="3">
         <v>-2800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="L23" s="3">
         <v>-4600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="M23" s="3">
         <v>-3400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="N23" s="3">
         <v>74400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="O23" s="3">
         <v>52200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="P23" s="3">
         <v>-24100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="Q23" s="3">
         <v>2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="R23" s="3">
         <v>22900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="S23" s="3">
         <v>33200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="T23" s="3">
         <v>5100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="U23" s="3">
         <v>8200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="W23" s="3">
         <v>-700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="X23" s="3">
         <v>-4900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="Y23" s="3">
         <v>-9900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="Z23" s="3">
         <v>-20200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="AA23" s="3">
         <v>-13000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="AB23" s="3">
         <v>-10200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="AC23" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AD23" s="3">
         <v>-23500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AE23" s="3">
         <v>-20900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AF23" s="3">
         <v>-20500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AG23" s="3">
         <v>-20300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AH23" s="3">
         <v>-22400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AI23" s="3">
         <v>-17900</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2003,58 +2232,58 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-46100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="O24" s="3">
         <v>-20500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="P24" s="3">
         <v>2900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="R24" s="3">
         <v>-8900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="S24" s="3">
         <v>1600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
-      </c>
-      <c r="S24" s="3">
-        <v>200</v>
-      </c>
-      <c r="T24" s="3">
-        <v>200</v>
-      </c>
-      <c r="U24" s="3">
-        <v>100</v>
-      </c>
-      <c r="V24" s="3">
-        <v>100</v>
-      </c>
-      <c r="W24" s="3">
-        <v>100</v>
       </c>
       <c r="X24" s="3">
         <v>200</v>
@@ -2066,19 +2295,34 @@
         <v>100</v>
       </c>
       <c r="AA24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB24" s="3">
         <v>100</v>
       </c>
       <c r="AC24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2407,225 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="K26" s="3">
         <v>-2800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="L26" s="3">
         <v>-4600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="M26" s="3">
         <v>-3400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="N26" s="3">
         <v>120600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="O26" s="3">
         <v>72700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="P26" s="3">
         <v>-27000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="Q26" s="3">
         <v>1200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="R26" s="3">
         <v>31800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="S26" s="3">
         <v>31600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="T26" s="3">
         <v>4800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="U26" s="3">
         <v>8000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="V26" s="3">
         <v>-500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="W26" s="3">
         <v>-900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="X26" s="3">
         <v>-5100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="Y26" s="3">
         <v>-10100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="Z26" s="3">
         <v>-20300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="AA26" s="3">
         <v>-13100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="AB26" s="3">
         <v>-10300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AC26" s="3">
         <v>-16200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AD26" s="3">
         <v>-23700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AE26" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AF26" s="3">
         <v>-20700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AG26" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AH26" s="3">
         <v>-22400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AI26" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I27" s="3">
         <v>-2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="K27" s="3">
         <v>-2800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="L27" s="3">
         <v>-4600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="M27" s="3">
         <v>-3400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="N27" s="3">
         <v>120600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="O27" s="3">
         <v>72700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="P27" s="3">
         <v>-27000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="Q27" s="3">
         <v>1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="R27" s="3">
         <v>31800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="S27" s="3">
         <v>31600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="T27" s="3">
         <v>4800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="U27" s="3">
         <v>8000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="V27" s="3">
         <v>-500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="W27" s="3">
         <v>-900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="X27" s="3">
         <v>-5100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="Y27" s="3">
         <v>-10100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="Z27" s="3">
         <v>-20300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="AA27" s="3">
         <v>-13100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="AB27" s="3">
         <v>-10300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AC27" s="3">
         <v>-16200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AD27" s="3">
         <v>-23700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AE27" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AF27" s="3">
         <v>-20700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AG27" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AH27" s="3">
         <v>-22400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AI27" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2710,23 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2430,46 +2734,46 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-1600</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-10400</v>
       </c>
-      <c r="H29" s="3">
+      <c r="M29" s="3">
         <v>-17700</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2477,11 +2781,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>16</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2492,11 +2796,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
@@ -2507,8 +2811,23 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2912,23 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,180 +3013,225 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="J32" s="3">
+        <v>100</v>
+      </c>
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="N32" s="3">
         <v>-25100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="O32" s="3">
         <v>6200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="P32" s="3">
         <v>-9600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="Q32" s="3">
         <v>-1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="R32" s="3">
         <v>-11900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="S32" s="3">
         <v>-11700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="T32" s="3">
         <v>-1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="U32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="Z32" s="3">
         <v>400</v>
-      </c>
-      <c r="V32" s="3">
-        <v>100</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="X32" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>800</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>200</v>
       </c>
       <c r="AA32" s="3">
         <v>100</v>
       </c>
       <c r="AB32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AH32" s="3">
         <v>400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AI32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I33" s="3">
         <v>-2400</v>
       </c>
-      <c r="E33" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="J33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K33" s="3">
         <v>-2800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="L33" s="3">
         <v>-15000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="M33" s="3">
         <v>-21200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="N33" s="3">
         <v>120600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="O33" s="3">
         <v>72700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="P33" s="3">
         <v>-27000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="Q33" s="3">
         <v>1200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="R33" s="3">
         <v>31800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="S33" s="3">
         <v>31600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="T33" s="3">
         <v>4800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="U33" s="3">
         <v>8000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="V33" s="3">
         <v>-500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="W33" s="3">
         <v>-900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="X33" s="3">
         <v>-5100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="Y33" s="3">
         <v>-10100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="Z33" s="3">
         <v>-20300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="AA33" s="3">
         <v>-13100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="AB33" s="3">
         <v>-10300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AC33" s="3">
         <v>-16200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AD33" s="3">
         <v>-23700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AE33" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AF33" s="3">
         <v>-20700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AG33" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AH33" s="3">
         <v>-22400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AI33" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3316,230 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I35" s="3">
         <v>-2400</v>
       </c>
-      <c r="E35" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="J35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K35" s="3">
         <v>-2800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="L35" s="3">
         <v>-15000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="M35" s="3">
         <v>-21200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="N35" s="3">
         <v>120600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="O35" s="3">
         <v>72700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="P35" s="3">
         <v>-27000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="Q35" s="3">
         <v>1200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="R35" s="3">
         <v>31800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="S35" s="3">
         <v>31600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="T35" s="3">
         <v>4800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="U35" s="3">
         <v>8000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="V35" s="3">
         <v>-500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="W35" s="3">
         <v>-900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="X35" s="3">
         <v>-5100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="Y35" s="3">
         <v>-10100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="Z35" s="3">
         <v>-20300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="AA35" s="3">
         <v>-13100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="AB35" s="3">
         <v>-10300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="AC35" s="3">
         <v>-16200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AD35" s="3">
         <v>-23700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AE35" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AF35" s="3">
         <v>-20700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AG35" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AH35" s="3">
         <v>-22400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AI35" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="I38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="K38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="M38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="O38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="W38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3570,13 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,180 +3607,215 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>23700</v>
+        <v>16700</v>
       </c>
       <c r="E41" s="3">
-        <v>23100</v>
+        <v>17400</v>
       </c>
       <c r="F41" s="3">
         <v>21300</v>
       </c>
       <c r="G41" s="3">
+        <v>20000</v>
+      </c>
+      <c r="H41" s="3">
+        <v>16900</v>
+      </c>
+      <c r="I41" s="3">
+        <v>18800</v>
+      </c>
+      <c r="J41" s="3">
+        <v>18200</v>
+      </c>
+      <c r="K41" s="3">
+        <v>21300</v>
+      </c>
+      <c r="L41" s="3">
         <v>21100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="M41" s="3">
         <v>54900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="N41" s="3">
         <v>41300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="O41" s="3">
         <v>624900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="P41" s="3">
         <v>842900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="Q41" s="3">
         <v>769300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="R41" s="3">
         <v>804100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="S41" s="3">
         <v>595900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="T41" s="3">
         <v>79200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="U41" s="3">
         <v>85800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="V41" s="3">
         <v>76800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="W41" s="3">
         <v>68000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="X41" s="3">
         <v>67600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="Y41" s="3">
         <v>67100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="Z41" s="3">
         <v>83600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="AA41" s="3">
         <v>85900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="AB41" s="3">
         <v>77100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AC41" s="3">
         <v>74400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AD41" s="3">
         <v>77600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AE41" s="3">
         <v>85900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AF41" s="3">
         <v>104100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AG41" s="3">
         <v>96500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AH41" s="3">
         <v>94100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AI41" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>16</v>
+      <c r="D42" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F42" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G42" s="3">
+        <v>2900</v>
       </c>
       <c r="H42" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I42" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J42" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M42" s="3">
         <v>48000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="N42" s="3">
         <v>90700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="O42" s="3">
         <v>610800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="P42" s="3">
         <v>387900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="Q42" s="3">
         <v>449000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="R42" s="3">
         <v>509600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="S42" s="3">
         <v>441900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="T42" s="3">
         <v>65100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="U42" s="3">
         <v>71400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="V42" s="3">
         <v>71500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="W42" s="3">
         <v>71500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="X42" s="3">
         <v>52500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="Y42" s="3">
         <v>39000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="Z42" s="3">
         <v>19800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="AA42" s="3">
         <v>9500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="AB42" s="3">
         <v>7100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="AC42" s="3">
         <v>4300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AD42" s="3">
         <v>14900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AE42" s="3">
         <v>11600</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AD42" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3362,7 +3826,7 @@
         <v>16</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>16</v>
@@ -3379,17 +3843,17 @@
       <c r="K43" s="3">
         <v>0</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -3436,16 +3900,31 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>16</v>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>16</v>
@@ -3453,272 +3932,317 @@
       <c r="G44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M44" s="3">
         <v>200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="N44" s="3">
         <v>200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="O44" s="3">
         <v>1700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="P44" s="3">
         <v>1900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="Q44" s="3">
         <v>1100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="R44" s="3">
         <v>1900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="S44" s="3">
         <v>1600</v>
-      </c>
-      <c r="O44" s="3">
-        <v>100</v>
-      </c>
-      <c r="P44" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3">
-        <v>100</v>
-      </c>
-      <c r="S44" s="3">
-        <v>0</v>
       </c>
       <c r="T44" s="3">
         <v>100</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X44" s="3" t="s">
-        <v>16</v>
+      <c r="U44" s="3">
+        <v>100</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>100</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
       </c>
       <c r="Y44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="Z44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>3300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>3500</v>
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F45" s="3">
+        <v>4600</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="3">
+        <v>300</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K45" s="3">
         <v>4400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="L45" s="3">
         <v>5000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="M45" s="3">
         <v>22500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="N45" s="3">
         <v>19200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="O45" s="3">
         <v>295300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="P45" s="3">
         <v>327500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="Q45" s="3">
         <v>314700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="R45" s="3">
         <v>302100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="S45" s="3">
         <v>292100</v>
-      </c>
-      <c r="O45" s="3">
-        <v>39500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>39100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>39500</v>
-      </c>
-      <c r="R45" s="3">
-        <v>39600</v>
-      </c>
-      <c r="S45" s="3">
-        <v>40300</v>
       </c>
       <c r="T45" s="3">
         <v>39500</v>
       </c>
       <c r="U45" s="3">
+        <v>39100</v>
+      </c>
+      <c r="V45" s="3">
+        <v>39500</v>
+      </c>
+      <c r="W45" s="3">
+        <v>39600</v>
+      </c>
+      <c r="X45" s="3">
+        <v>40300</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>39500</v>
+      </c>
+      <c r="Z45" s="3">
         <v>35200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="AA45" s="3">
         <v>34100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="AB45" s="3">
         <v>28300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="AC45" s="3">
         <v>24900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AD45" s="3">
         <v>12600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AE45" s="3">
         <v>12600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AF45" s="3">
         <v>9700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AG45" s="3">
         <v>10900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AH45" s="3">
         <v>9600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AI45" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>29600</v>
+      </c>
+      <c r="F46" s="3">
+        <v>29800</v>
+      </c>
+      <c r="G46" s="3">
+        <v>28600</v>
+      </c>
+      <c r="H46" s="3">
+        <v>26900</v>
+      </c>
+      <c r="I46" s="3">
         <v>27000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="J46" s="3">
         <v>26600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="K46" s="3">
         <v>25700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="L46" s="3">
         <v>26100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="M46" s="3">
         <v>125500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="N46" s="3">
         <v>151300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="O46" s="3">
         <v>1532700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="P46" s="3">
         <v>1560200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="Q46" s="3">
         <v>1534000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="R46" s="3">
         <v>1617700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="S46" s="3">
         <v>1331400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="T46" s="3">
         <v>184000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="U46" s="3">
         <v>196500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="V46" s="3">
         <v>187800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="W46" s="3">
         <v>179300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="X46" s="3">
         <v>160400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="Y46" s="3">
         <v>145600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="Z46" s="3">
         <v>138600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="AA46" s="3">
         <v>129600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="AB46" s="3">
         <v>112400</v>
-      </c>
-      <c r="X46" s="3">
-        <v>103700</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>105100</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>110000</v>
-      </c>
-      <c r="AA46" s="3">
-        <v>113900</v>
-      </c>
-      <c r="AB46" s="3">
-        <v>107400</v>
       </c>
       <c r="AC46" s="3">
         <v>103700</v>
       </c>
       <c r="AD46" s="3">
+        <v>105100</v>
+      </c>
+      <c r="AE46" s="3">
+        <v>110000</v>
+      </c>
+      <c r="AF46" s="3">
+        <v>113900</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>107400</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>103700</v>
+      </c>
+      <c r="AI46" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3780,13 +4304,28 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>700</v>
+        <v>1600</v>
       </c>
       <c r="E48" s="3">
         <v>800</v>
@@ -3795,84 +4334,99 @@
         <v>900</v>
       </c>
       <c r="G48" s="3">
+        <v>700</v>
+      </c>
+      <c r="H48" s="3">
+        <v>700</v>
+      </c>
+      <c r="I48" s="3">
+        <v>700</v>
+      </c>
+      <c r="J48" s="3">
+        <v>800</v>
+      </c>
+      <c r="K48" s="3">
+        <v>900</v>
+      </c>
+      <c r="L48" s="3">
         <v>100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="M48" s="3">
         <v>6600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="N48" s="3">
         <v>8500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="O48" s="3">
         <v>86300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="P48" s="3">
         <v>144000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="Q48" s="3">
         <v>144000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="R48" s="3">
         <v>119200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="S48" s="3">
         <v>89300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="T48" s="3">
         <v>12000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="U48" s="3">
         <v>12800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="V48" s="3">
         <v>12100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="W48" s="3">
         <v>13900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="X48" s="3">
         <v>11600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="Y48" s="3">
         <v>11600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="Z48" s="3">
         <v>5100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="AA48" s="3">
         <v>5000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="AB48" s="3">
         <v>5500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="AC48" s="3">
         <v>6500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AD48" s="3">
         <v>7300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AE48" s="3">
         <v>7100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AF48" s="3">
         <v>5900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AG48" s="3">
         <v>5800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AH48" s="3">
         <v>6000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AI48" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
         <v>100</v>
@@ -3884,76 +4438,91 @@
         <v>100</v>
       </c>
       <c r="H49" s="3">
+        <v>100</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>100</v>
+      </c>
+      <c r="K49" s="3">
+        <v>100</v>
+      </c>
+      <c r="L49" s="3">
+        <v>100</v>
+      </c>
+      <c r="M49" s="3">
         <v>1600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="N49" s="3">
         <v>1800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="O49" s="3">
         <v>12200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="P49" s="3">
         <v>44900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="Q49" s="3">
         <v>23000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="R49" s="3">
         <v>24500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="S49" s="3">
         <v>12300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="T49" s="3">
         <v>1900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="U49" s="3">
         <v>2000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="V49" s="3">
         <v>2200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="W49" s="3">
         <v>2000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="X49" s="3">
         <v>2100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="Y49" s="3">
         <v>2300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="Z49" s="3">
         <v>2300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="AA49" s="3">
         <v>2300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="AB49" s="3">
         <v>1900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="AC49" s="3">
         <v>1900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AD49" s="3">
         <v>2100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AE49" s="3">
         <v>2200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AF49" s="3">
         <v>1500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AG49" s="3">
         <v>1400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AH49" s="3">
         <v>1300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AI49" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4607,23 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,13 +4708,28 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
@@ -4139,79 +4738,94 @@
         <v>300</v>
       </c>
       <c r="G52" s="3">
+        <v>400</v>
+      </c>
+      <c r="H52" s="3">
+        <v>300</v>
+      </c>
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
+        <v>200</v>
+      </c>
+      <c r="K52" s="3">
+        <v>300</v>
+      </c>
+      <c r="L52" s="3">
+        <v>200</v>
+      </c>
+      <c r="M52" s="3">
         <v>23700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="N52" s="3">
         <v>25600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="O52" s="3">
         <v>71300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="P52" s="3">
         <v>447000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="Q52" s="3">
         <v>543600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="R52" s="3">
         <v>448200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="S52" s="3">
         <v>573500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="T52" s="3">
         <v>67400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="U52" s="3">
         <v>35600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="V52" s="3">
         <v>19000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="W52" s="3">
         <v>1100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="X52" s="3">
         <v>1200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="Y52" s="3">
         <v>900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="Z52" s="3">
         <v>600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="AA52" s="3">
         <v>1800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="AB52" s="3">
         <v>1700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="AC52" s="3">
         <v>1700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AD52" s="3">
         <v>1800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AE52" s="3">
         <v>1800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AF52" s="3">
         <v>2100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AG52" s="3">
         <v>1800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AH52" s="3">
         <v>1800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AI52" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,94 +4910,124 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>30800</v>
+      </c>
+      <c r="F54" s="3">
+        <v>31200</v>
+      </c>
+      <c r="G54" s="3">
+        <v>29800</v>
+      </c>
+      <c r="H54" s="3">
+        <v>27900</v>
+      </c>
+      <c r="I54" s="3">
         <v>28000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="J54" s="3">
         <v>27600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="K54" s="3">
         <v>26900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="L54" s="3">
         <v>26500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="M54" s="3">
         <v>157400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="N54" s="3">
         <v>187100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="O54" s="3">
         <v>1702400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="P54" s="3">
         <v>2196100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="Q54" s="3">
         <v>2244500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="R54" s="3">
         <v>2209500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="S54" s="3">
         <v>2006600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="T54" s="3">
         <v>265300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="U54" s="3">
         <v>246900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="V54" s="3">
         <v>221200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="W54" s="3">
         <v>196300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="X54" s="3">
         <v>175300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="Y54" s="3">
         <v>160400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="Z54" s="3">
         <v>146700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="AA54" s="3">
         <v>138700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="AB54" s="3">
         <v>121500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="AC54" s="3">
         <v>113800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AD54" s="3">
         <v>116300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AE54" s="3">
         <v>121100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AF54" s="3">
         <v>123300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AG54" s="3">
         <v>116300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AH54" s="3">
         <v>112800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AI54" s="3">
         <v>105500</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +5058,13 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,31 +5095,36 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -4532,31 +5186,46 @@
       <c r="AD57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4577,226 +5246,271 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>2600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="W58" s="3">
         <v>4700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="X58" s="3">
         <v>6500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="Y58" s="3">
         <v>8300</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB58" s="3">
         <v>3500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="AC58" s="3">
         <v>800</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>23000</v>
+        <v>38900</v>
       </c>
       <c r="E59" s="3">
-        <v>20500</v>
+        <v>34500</v>
       </c>
       <c r="F59" s="3">
+        <v>32600</v>
+      </c>
+      <c r="G59" s="3">
+        <v>26300</v>
+      </c>
+      <c r="H59" s="3">
+        <v>21200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>18600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>15800</v>
+      </c>
+      <c r="K59" s="3">
         <v>17800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="L59" s="3">
         <v>14800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="M59" s="3">
         <v>291100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="N59" s="3">
         <v>2047300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="O59" s="3">
         <v>2452600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="P59" s="3">
         <v>3000500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="Q59" s="3">
         <v>3050200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="R59" s="3">
         <v>3018100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="S59" s="3">
         <v>2842300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="T59" s="3">
         <v>392700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="U59" s="3">
         <v>396400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="V59" s="3">
         <v>378900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="W59" s="3">
         <v>346200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="X59" s="3">
         <v>324900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="Y59" s="3">
         <v>304100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="Z59" s="3">
         <v>273800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="AA59" s="3">
         <v>245200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="AB59" s="3">
         <v>221500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="AC59" s="3">
         <v>210900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AD59" s="3">
         <v>211400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AE59" s="3">
         <v>192100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AF59" s="3">
         <v>172400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AG59" s="3">
         <v>143000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AH59" s="3">
         <v>122000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AI59" s="3">
         <v>97500</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>42500</v>
+      </c>
+      <c r="F60" s="3">
+        <v>39100</v>
+      </c>
+      <c r="G60" s="3">
+        <v>32200</v>
+      </c>
+      <c r="H60" s="3">
+        <v>26400</v>
+      </c>
+      <c r="I60" s="3">
         <v>23000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="J60" s="3">
         <v>20500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="K60" s="3">
         <v>17800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="L60" s="3">
         <v>14800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="M60" s="3">
         <v>291100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="N60" s="3">
         <v>297000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="O60" s="3">
         <v>2452600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="P60" s="3">
         <v>3000500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="Q60" s="3">
         <v>3050200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="R60" s="3">
         <v>3018100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="S60" s="3">
         <v>2842300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="T60" s="3">
         <v>392700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="U60" s="3">
         <v>396400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="V60" s="3">
         <v>381600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="W60" s="3">
         <v>350800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="X60" s="3">
         <v>331400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="Y60" s="3">
         <v>312500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="Z60" s="3">
         <v>273800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="AA60" s="3">
         <v>245200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="AB60" s="3">
         <v>225000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="AC60" s="3">
         <v>211700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AD60" s="3">
         <v>211400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AE60" s="3">
         <v>192100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AF60" s="3">
         <v>172400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AG60" s="3">
         <v>143000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AH60" s="3">
         <v>122000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AI60" s="3">
         <v>97500</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -4808,13 +5522,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4847,26 +5561,26 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>10000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="AA61" s="3">
         <v>11100</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -4876,94 +5590,124 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>500</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K62" s="3">
         <v>600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="L62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="M62" s="3">
         <v>3000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="N62" s="3">
         <v>3500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="O62" s="3">
         <v>38100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="P62" s="3">
         <v>62200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="Q62" s="3">
         <v>62700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="R62" s="3">
         <v>58400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="S62" s="3">
         <v>33700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="T62" s="3">
         <v>4700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="U62" s="3">
         <v>5100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="V62" s="3">
         <v>4700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="W62" s="3">
         <v>5600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="X62" s="3">
         <v>3900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="Y62" s="3">
         <v>4200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="Z62" s="3">
         <v>2600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="AA62" s="3">
         <v>3600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="AB62" s="3">
         <v>3000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="AC62" s="3">
         <v>3700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AD62" s="3">
         <v>4100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AE62" s="3">
         <v>5000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AF62" s="3">
         <v>6000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AG62" s="3">
         <v>7000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AH62" s="3">
         <v>5200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AI62" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5792,23 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5893,23 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,94 +5994,124 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>42800</v>
+      </c>
+      <c r="F66" s="3">
+        <v>39300</v>
+      </c>
+      <c r="G66" s="3">
+        <v>32400</v>
+      </c>
+      <c r="H66" s="3">
+        <v>26700</v>
+      </c>
+      <c r="I66" s="3">
         <v>23500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="J66" s="3">
         <v>21100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="K66" s="3">
         <v>18400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="L66" s="3">
         <v>15100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="M66" s="3">
         <v>294100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="N66" s="3">
         <v>300500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="O66" s="3">
         <v>2490600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="P66" s="3">
         <v>3062700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="Q66" s="3">
         <v>3112900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="R66" s="3">
         <v>3076500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="S66" s="3">
         <v>2876000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="T66" s="3">
         <v>397400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="U66" s="3">
         <v>401500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="V66" s="3">
         <v>386300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="W66" s="3">
         <v>356500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="X66" s="3">
         <v>335300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="Y66" s="3">
         <v>316700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="Z66" s="3">
         <v>286500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="AA66" s="3">
         <v>260000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="AB66" s="3">
         <v>228000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AC66" s="3">
         <v>215500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AD66" s="3">
         <v>215500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AE66" s="3">
         <v>197000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AF66" s="3">
         <v>178400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AG66" s="3">
         <v>150100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AH66" s="3">
         <v>127200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AI66" s="3">
         <v>101800</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +6142,13 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +6233,23 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +6334,23 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5596,8 +6435,23 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,61 +6536,76 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-346400</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="3">
         <v>-331200</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N72" s="3">
         <v>-1931400</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
-      <c r="T72" s="3">
-        <v>0</v>
+      <c r="P72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U72" s="3">
         <v>0</v>
@@ -5744,32 +6613,47 @@
       <c r="V72" s="3">
         <v>0</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>16</v>
+      <c r="W72" s="3">
+        <v>0</v>
+      </c>
+      <c r="X72" s="3">
+        <v>0</v>
       </c>
       <c r="Y72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD72" s="3">
         <v>-260300</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH72" s="3">
         <v>-170600</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6738,23 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6839,23 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,94 +6940,124 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="F76" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="G76" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="H76" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I76" s="3">
         <v>4500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="J76" s="3">
         <v>6600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="K76" s="3">
         <v>8500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="L76" s="3">
         <v>11400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="M76" s="3">
         <v>-136700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="N76" s="3">
         <v>-113400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="O76" s="3">
         <v>-788200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="P76" s="3">
         <v>-866600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="Q76" s="3">
         <v>-868300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="R76" s="3">
         <v>-866900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="S76" s="3">
         <v>-869400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="T76" s="3">
         <v>-132000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="U76" s="3">
         <v>-154700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="V76" s="3">
         <v>-165100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="W76" s="3">
         <v>-160200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="X76" s="3">
         <v>-160000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="Y76" s="3">
         <v>-156300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="Z76" s="3">
         <v>-139800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="AA76" s="3">
         <v>-121200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="AB76" s="3">
         <v>-106500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AC76" s="3">
         <v>-101700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AD76" s="3">
         <v>-99200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AE76" s="3">
         <v>-75900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AF76" s="3">
         <v>-55000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AG76" s="3">
         <v>-33700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AH76" s="3">
         <v>-14400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AI76" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +7142,230 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="I80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="K80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="M80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="O80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="W80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I81" s="3">
         <v>-2400</v>
       </c>
-      <c r="E81" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="J81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K81" s="3">
         <v>-2800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="L81" s="3">
         <v>-15000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="M81" s="3">
         <v>-21200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="N81" s="3">
         <v>120600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="O81" s="3">
         <v>72700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="P81" s="3">
         <v>-27000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="Q81" s="3">
         <v>1200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="R81" s="3">
         <v>31800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="S81" s="3">
         <v>31600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="T81" s="3">
         <v>4800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="U81" s="3">
         <v>8000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="V81" s="3">
         <v>-500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="W81" s="3">
         <v>-900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="X81" s="3">
         <v>-5100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="Y81" s="3">
         <v>-10100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="Z81" s="3">
         <v>-20300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="AA81" s="3">
         <v>-13100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="AB81" s="3">
         <v>-10300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="AC81" s="3">
         <v>-16200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AD81" s="3">
         <v>-23700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AE81" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AF81" s="3">
         <v>-20700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AG81" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AH81" s="3">
         <v>-22400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AI81" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,31 +7396,36 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -6493,8 +7487,23 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +7588,23 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +7689,23 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +7790,23 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7891,23 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,31 +7992,46 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -7009,8 +8093,23 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,31 +8140,36 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -7127,8 +8231,23 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +8332,23 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,31 +8433,46 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -7385,8 +8534,23 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,31 +8581,36 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7503,8 +8672,23 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +8773,23 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +8874,23 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,31 +8975,46 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -7847,31 +9076,46 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7933,31 +9177,46 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -8017,6 +9276,21 @@
         <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>COE</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E8" s="3">
         <v>11000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2181500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>573600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>579800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>92400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>535100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>538500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>72700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>76800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>62000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>62900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>53900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>48700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>43300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>44000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>39400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>37700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>38700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>35000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>28500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>23200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>18600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E9" s="3">
         <v>2400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2100</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1900</v>
       </c>
       <c r="G9" s="3">
         <v>1900</v>
       </c>
       <c r="H9" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I9" s="3">
         <v>1400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>558000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>151900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>158100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>24600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>146100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>146700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>21200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>22700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>17500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>17900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>16400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>16100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>15900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>14500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>13400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>10600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>8000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>6600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E10" s="3">
         <v>8600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1623500</v>
-      </c>
-      <c r="O10" s="3">
-        <v>421700</v>
       </c>
       <c r="P10" s="3">
         <v>421700</v>
       </c>
       <c r="Q10" s="3">
+        <v>421700</v>
+      </c>
+      <c r="R10" s="3">
         <v>67800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>389000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>391800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>51600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>54100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>44500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>45100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>37400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>32600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>27100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>28100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>25900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>24300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>24100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>21700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>17900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>15200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>12000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1157,91 +1171,94 @@
         <v>900</v>
       </c>
       <c r="H12" s="3">
+        <v>900</v>
+      </c>
+      <c r="I12" s="3">
         <v>700</v>
-      </c>
-      <c r="I12" s="3">
-        <v>400</v>
       </c>
       <c r="J12" s="3">
         <v>400</v>
       </c>
       <c r="K12" s="3">
+        <v>400</v>
+      </c>
+      <c r="L12" s="3">
         <v>600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>178800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>40700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>65000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>44600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>43800</v>
-      </c>
-      <c r="T12" s="3">
-        <v>5700</v>
       </c>
       <c r="U12" s="3">
         <v>5700</v>
       </c>
       <c r="V12" s="3">
+        <v>5700</v>
+      </c>
+      <c r="W12" s="3">
         <v>5800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6300</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>6200</v>
       </c>
       <c r="Z12" s="3">
         <v>6200</v>
       </c>
       <c r="AA12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="AB12" s="3">
         <v>6600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>6200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>9000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>9100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>7500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>7400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>6700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1341,8 +1358,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1373,51 +1393,51 @@
       <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>21500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>31800</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-7400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-7600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-1000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-1600</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>16</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>1100</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1433,8 +1453,8 @@
       <c r="AF14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1442,8 +1462,11 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>13400</v>
+        <v>17100</v>
       </c>
       <c r="E17" s="3">
         <v>13400</v>
       </c>
       <c r="F17" s="3">
+        <v>13400</v>
+      </c>
+      <c r="G17" s="3">
         <v>11800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7900</v>
-      </c>
-      <c r="J17" s="3">
-        <v>7200</v>
       </c>
       <c r="K17" s="3">
         <v>7200</v>
       </c>
       <c r="L17" s="3">
+        <v>7200</v>
+      </c>
+      <c r="M17" s="3">
         <v>7600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2132200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>515200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>613600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>91500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>524100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>517100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>68700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>69800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>63000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>64000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>59200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>58400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>63100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>56900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>50100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>53500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>61400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>55800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>48900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>43600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>40600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>49300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>58400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-33800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>21400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7100</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-1000</v>
       </c>
       <c r="W18" s="3">
         <v>-1000</v>
       </c>
       <c r="X18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-19800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-12900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-10700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-15900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-22700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-20700</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>-20400</v>
       </c>
       <c r="AG18" s="3">
         <v>-20400</v>
       </c>
       <c r="AH18" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="AI18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1816,136 +1849,140 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>25100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>9600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>11900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>11700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>16</v>
       </c>
@@ -2018,8 +2055,11 @@
       <c r="AI21" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2050,11 +2090,11 @@
       <c r="L22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>16</v>
+      <c r="M22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>16</v>
@@ -2062,17 +2102,17 @@
       <c r="P22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>16</v>
+      <c r="Q22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -2119,130 +2159,136 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>74400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>52200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-24100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>22900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>33200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>8200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-20200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-10200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-23500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-20900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-20500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-20300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-22400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-17900</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -2256,28 +2302,28 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-46100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-20500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-8900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
-      </c>
-      <c r="U24" s="3">
-        <v>200</v>
       </c>
       <c r="V24" s="3">
         <v>200</v>
@@ -2292,7 +2338,7 @@
         <v>200</v>
       </c>
       <c r="Z24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA24" s="3">
         <v>100</v>
@@ -2301,19 +2347,19 @@
         <v>100</v>
       </c>
       <c r="AC24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD24" s="3">
         <v>200</v>
       </c>
       <c r="AE24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>200</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>100</v>
       </c>
       <c r="AH24" s="3">
         <v>100</v>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>100</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>120600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>72700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>31800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>31600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>8000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-10300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-16200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-23700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-21000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-20700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-20400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-22400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>120600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>72700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>31800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>31600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-10300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-16200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-23700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-21000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-20700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-20400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-22400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2755,14 +2816,14 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-10400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-17700</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O29" s="3" t="s">
         <v>16</v>
       </c>
@@ -2775,8 +2836,8 @@
       <c r="R29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2796,14 +2857,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>16</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
         <v>1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-25100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-11900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-11700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-21200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>120600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>72700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>31800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>31600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-10300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-16200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-23700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-21000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-20700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-20400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-22400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-21200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>120600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>72700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>31800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>31600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-10300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-16200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-23700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-21000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-20700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-20400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-22400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,199 +3698,203 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E41" s="3">
         <v>16700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>21300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>54900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>41300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>624900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>842900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>769300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>804100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>595900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>79200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>85800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>76800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>68000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>67600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>67100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>83600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>85900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>77100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>74400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>77600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>85900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>104100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>96500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>94100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4300</v>
+        <v>1400</v>
       </c>
       <c r="E42" s="3">
         <v>4300</v>
       </c>
       <c r="F42" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G42" s="3">
         <v>2100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4800</v>
-      </c>
-      <c r="I42" s="3">
-        <v>4900</v>
       </c>
       <c r="J42" s="3">
         <v>4900</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>16</v>
+      <c r="K42" s="3">
+        <v>4900</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M42" s="3">
+      <c r="M42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N42" s="3">
         <v>48000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>90700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>610800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>387900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>449000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>509600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>441900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>65100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>71400</v>
-      </c>
-      <c r="V42" s="3">
-        <v>71500</v>
       </c>
       <c r="W42" s="3">
         <v>71500</v>
       </c>
       <c r="X42" s="3">
+        <v>71500</v>
+      </c>
+      <c r="Y42" s="3">
         <v>52500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>39000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>19800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>9500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>7100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>4300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>14900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>11600</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3814,8 +3904,11 @@
       <c r="AI42" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3825,12 +3918,12 @@
       <c r="E43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3840,11 +3933,11 @@
       <c r="J43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>16</v>
+      <c r="K43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>16</v>
@@ -3855,8 +3948,8 @@
       <c r="O43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -3915,19 +4008,22 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E44" s="3">
         <v>0</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>16</v>
+      <c r="F44" s="3">
+        <v>0</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>16</v>
@@ -3947,48 +4043,48 @@
       <c r="L44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M44" s="3">
-        <v>200</v>
+      <c r="M44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N44" s="3">
         <v>200</v>
       </c>
       <c r="O44" s="3">
+        <v>200</v>
+      </c>
+      <c r="P44" s="3">
         <v>1700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1600</v>
-      </c>
-      <c r="T44" s="3">
-        <v>100</v>
       </c>
       <c r="U44" s="3">
         <v>100</v>
       </c>
       <c r="V44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
         <v>100</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
-      </c>
       <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3">
         <v>100</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3998,8 +4094,8 @@
       <c r="AC44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AD44" s="3">
-        <v>0</v>
+      <c r="AD44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AE44" s="3">
         <v>0</v>
@@ -4016,8 +4112,11 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4027,199 +4126,205 @@
       <c r="E45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="3">
         <v>4600</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K45" s="3">
         <v>2800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>22500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>19200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>295300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>327500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>314700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>302100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>292100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>39500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>39100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>39500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>39600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>40300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>39500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>35200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>34100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>28300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>24900</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>12600</v>
       </c>
       <c r="AE45" s="3">
         <v>12600</v>
       </c>
       <c r="AF45" s="3">
+        <v>12600</v>
+      </c>
+      <c r="AG45" s="3">
         <v>9700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>10900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>9600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E46" s="3">
         <v>31500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>29600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>28600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>26900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>27000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>26600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>26100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>125500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>151300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1532700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1560200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1534000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1617700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1331400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>184000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>196500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>187800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>179300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>160400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>145600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>138600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>129600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>112400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>103700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>105100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>110000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>113900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>107400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>103700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4244,8 +4349,8 @@
       <c r="J47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4319,22 +4424,25 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>900</v>
-      </c>
-      <c r="G48" s="3">
-        <v>700</v>
       </c>
       <c r="H48" s="3">
         <v>700</v>
@@ -4343,85 +4451,88 @@
         <v>700</v>
       </c>
       <c r="J48" s="3">
+        <v>700</v>
+      </c>
+      <c r="K48" s="3">
         <v>800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>86300</v>
-      </c>
-      <c r="P48" s="3">
-        <v>144000</v>
       </c>
       <c r="Q48" s="3">
         <v>144000</v>
       </c>
       <c r="R48" s="3">
+        <v>144000</v>
+      </c>
+      <c r="S48" s="3">
         <v>119200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>89300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13900</v>
-      </c>
-      <c r="X48" s="3">
-        <v>11600</v>
       </c>
       <c r="Y48" s="3">
         <v>11600</v>
       </c>
       <c r="Z48" s="3">
+        <v>11600</v>
+      </c>
+      <c r="AA48" s="3">
         <v>5100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4441,10 +4552,10 @@
         <v>100</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>100</v>
@@ -4453,43 +4564,43 @@
         <v>100</v>
       </c>
       <c r="M49" s="3">
+        <v>100</v>
+      </c>
+      <c r="N49" s="3">
         <v>1600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>12200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>44900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>23000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>24500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>12300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2100</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>2300</v>
       </c>
       <c r="Z49" s="3">
         <v>2300</v>
@@ -4498,31 +4609,34 @@
         <v>2300</v>
       </c>
       <c r="AB49" s="3">
-        <v>1900</v>
+        <v>2300</v>
       </c>
       <c r="AC49" s="3">
         <v>1900</v>
       </c>
       <c r="AD49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AE49" s="3">
         <v>2100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>500</v>
+      </c>
+      <c r="E52" s="3">
         <v>300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>200</v>
       </c>
       <c r="J52" s="3">
         <v>200</v>
       </c>
       <c r="K52" s="3">
+        <v>200</v>
+      </c>
+      <c r="L52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>71300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>447000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>543600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>448200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>573500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>67400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>35600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>19000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1800</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>1700</v>
       </c>
       <c r="AC52" s="3">
         <v>1700</v>
       </c>
       <c r="AD52" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="AE52" s="3">
         <v>1800</v>
       </c>
       <c r="AF52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AG52" s="3">
         <v>2100</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>1800</v>
       </c>
       <c r="AH52" s="3">
         <v>1800</v>
       </c>
       <c r="AI52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E54" s="3">
         <v>33500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>28000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>26900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>157400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>187100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1702400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2196100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2244500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2209500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2006600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>265300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>246900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>221200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>196300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>175300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>160400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>146700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>138700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>121500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>113800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>116300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>121100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>123300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>116300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>112800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>105500</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,8 +5230,9 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5126,8 +5257,8 @@
       <c r="J57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -5201,34 +5332,37 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E58" s="3">
         <v>800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>600</v>
       </c>
       <c r="G58" s="3">
         <v>600</v>
       </c>
       <c r="H58" s="3">
+        <v>600</v>
+      </c>
+      <c r="I58" s="3">
         <v>500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>400</v>
       </c>
       <c r="J58" s="3">
         <v>400</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5261,32 +5395,32 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>2600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>6500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>8300</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC58" s="3">
         <v>3500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>800</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE58" s="3" t="s">
         <v>16</v>
       </c>
@@ -5302,219 +5436,228 @@
       <c r="AI58" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E59" s="3">
         <v>38900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>34500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>32600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>26300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>18600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>291100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2047300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2452600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3000500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3050200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3018100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2842300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>392700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>396400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>378900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>346200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>324900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>304100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>273800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>245200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>221500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>210900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>211400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>192100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>172400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>143000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>122000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>97500</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E60" s="3">
         <v>46000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>42500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>39100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>20500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>291100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>297000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2452600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3000500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3050200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3018100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2842300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>392700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>396400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>381600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>350800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>331400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>312500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>273800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>245200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>225000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>211700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>211400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>192100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>172400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>143000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>122000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>97500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E61" s="3">
         <v>500</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -5522,17 +5665,17 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5576,14 +5719,14 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>10000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>11100</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5605,13 +5748,16 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>16</v>
+      <c r="D62" s="3">
+        <v>300</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>16</v>
@@ -5631,83 +5777,86 @@
       <c r="J62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L62" s="3">
         <v>600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>38100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>62200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>62700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>58400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>33700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>4100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>7000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E66" s="3">
         <v>46800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>42800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>26700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>23500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>21100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>18400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>294100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>300500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2490600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3062700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3112900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3076500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2876000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>397400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>401500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>386300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>356500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>335300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>316700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>286500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>260000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>228000</v>
-      </c>
-      <c r="AC66" s="3">
-        <v>215500</v>
       </c>
       <c r="AD66" s="3">
         <v>215500</v>
       </c>
       <c r="AE66" s="3">
+        <v>215500</v>
+      </c>
+      <c r="AF66" s="3">
         <v>197000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>178400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>150100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>127200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>101800</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,8 +6722,11 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6562,36 +6736,36 @@
       <c r="E72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G72" s="3">
         <v>-346400</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K72" s="3">
         <v>-331200</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O72" s="3">
         <v>-1931400</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6607,8 +6781,8 @@
       <c r="T72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
+      <c r="U72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V72" s="3">
         <v>0</v>
@@ -6628,32 +6802,35 @@
       <c r="AA72" s="3">
         <v>0</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>16</v>
+      <c r="AB72" s="3">
+        <v>0</v>
       </c>
       <c r="AC72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE72" s="3">
         <v>-260300</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AG72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI72" s="3">
         <v>-170600</v>
       </c>
-      <c r="AI72" s="3" t="s">
+      <c r="AJ72" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-13600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-12300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-8300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-2600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-136700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-113400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-788200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-866600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-868300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-866900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-869400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-132000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-154700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-165100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-160200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-160000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-156300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-139800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-121200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-106500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-101700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-99200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-75900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-55000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-33700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-14400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-21200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>120600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>72700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>31800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>31600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-10100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-10300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-16200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-23700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-21000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-20700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-20400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-22400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7427,8 +7626,8 @@
       <c r="J83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,8 +8221,11 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8033,8 +8250,8 @@
       <c r="J89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -8108,8 +8325,11 @@
       <c r="AI89" s="3">
         <v>0</v>
       </c>
+      <c r="AJ89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,8 +8365,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8171,8 +8392,8 @@
       <c r="J91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -8246,8 +8467,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,8 +8675,11 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8474,8 +8704,8 @@
       <c r="J94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -8549,8 +8779,11 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8612,8 +8846,8 @@
       <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,8 +9233,11 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9016,8 +9262,8 @@
       <c r="J100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -9091,8 +9337,11 @@
       <c r="AI100" s="3">
         <v>0</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9117,8 +9366,8 @@
       <c r="J101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9192,8 +9441,11 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9218,8 +9470,8 @@
       <c r="J102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -9291,6 +9543,9 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/COE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>COE</t>
   </si>
@@ -662,12 +662,11 @@
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -708,22 +707,22 @@
         <v>45657</v>
       </c>
       <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45016</v>
       </c>
       <c r="K7" s="2">
         <v>44926</v>
@@ -812,22 +811,22 @@
         <v>16200</v>
       </c>
       <c r="E8" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F8" s="3">
         <v>11000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6300</v>
-      </c>
-      <c r="J8" s="3">
-        <v>5600</v>
       </c>
       <c r="K8" s="3">
         <v>5100</v>
@@ -916,22 +915,22 @@
         <v>3700</v>
       </c>
       <c r="E9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F9" s="3">
         <v>2400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2100</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1900</v>
       </c>
       <c r="H9" s="3">
         <v>1900</v>
       </c>
       <c r="I9" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J9" s="3">
         <v>1400</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1200</v>
       </c>
       <c r="K9" s="3">
         <v>1100</v>
@@ -1020,22 +1019,22 @@
         <v>12600</v>
       </c>
       <c r="E10" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F10" s="3">
         <v>8600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4900</v>
-      </c>
-      <c r="J10" s="3">
-        <v>4300</v>
       </c>
       <c r="K10" s="3">
         <v>4000</v>
@@ -1162,7 +1161,7 @@
         <v>900</v>
       </c>
       <c r="E12" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F12" s="3">
         <v>900</v>
@@ -1174,10 +1173,10 @@
         <v>900</v>
       </c>
       <c r="I12" s="3">
+        <v>900</v>
+      </c>
+      <c r="J12" s="3">
         <v>700</v>
-      </c>
-      <c r="J12" s="3">
-        <v>400</v>
       </c>
       <c r="K12" s="3">
         <v>400</v>
@@ -1613,22 +1612,22 @@
         <v>17100</v>
       </c>
       <c r="E17" s="3">
-        <v>13400</v>
+        <v>14800</v>
       </c>
       <c r="F17" s="3">
         <v>13400</v>
       </c>
       <c r="G17" s="3">
+        <v>13400</v>
+      </c>
+      <c r="H17" s="3">
         <v>11800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9200</v>
-      </c>
-      <c r="J17" s="3">
-        <v>7900</v>
       </c>
       <c r="K17" s="3">
         <v>7200</v>
@@ -1717,22 +1716,22 @@
         <v>-900</v>
       </c>
       <c r="E18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-2400</v>
       </c>
       <c r="K18" s="3">
         <v>-2200</v>
@@ -1859,22 +1858,22 @@
         <v>600</v>
       </c>
       <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
@@ -1963,22 +1962,22 @@
         <v>-1500</v>
       </c>
       <c r="E21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-5500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-2400</v>
       </c>
       <c r="K21" s="3">
         <v>-2000</v>
@@ -2171,22 +2170,22 @@
         <v>-1500</v>
       </c>
       <c r="E23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3000</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-2400</v>
       </c>
       <c r="K23" s="3">
         <v>-2000</v>
@@ -2275,22 +2274,22 @@
         <v>200</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2483,22 +2482,22 @@
         <v>-1700</v>
       </c>
       <c r="E26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2900</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-2400</v>
       </c>
       <c r="K26" s="3">
         <v>-2000</v>
@@ -2587,22 +2586,22 @@
         <v>-1600</v>
       </c>
       <c r="E27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-2400</v>
       </c>
       <c r="K27" s="3">
         <v>-2000</v>
@@ -3107,22 +3106,22 @@
         <v>-600</v>
       </c>
       <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
@@ -3211,22 +3210,22 @@
         <v>-1600</v>
       </c>
       <c r="E33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2900</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-2400</v>
       </c>
       <c r="K33" s="3">
         <v>-2000</v>
@@ -3419,22 +3418,22 @@
         <v>-1600</v>
       </c>
       <c r="E35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2900</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-2400</v>
       </c>
       <c r="K35" s="3">
         <v>-2000</v>
@@ -3528,22 +3527,22 @@
         <v>45657</v>
       </c>
       <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
-      </c>
-      <c r="J38" s="2">
-        <v>45016</v>
       </c>
       <c r="K38" s="2">
         <v>44926</v>
@@ -3708,22 +3707,22 @@
         <v>27800</v>
       </c>
       <c r="E41" s="3">
+        <v>22200</v>
+      </c>
+      <c r="F41" s="3">
         <v>16700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>21300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16900</v>
-      </c>
-      <c r="J41" s="3">
-        <v>18800</v>
       </c>
       <c r="K41" s="3">
         <v>18200</v>
@@ -3812,22 +3811,22 @@
         <v>1400</v>
       </c>
       <c r="E42" s="3">
-        <v>4300</v>
+        <v>3400</v>
       </c>
       <c r="F42" s="3">
         <v>4300</v>
       </c>
       <c r="G42" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H42" s="3">
         <v>2100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4800</v>
-      </c>
-      <c r="J42" s="3">
-        <v>4900</v>
       </c>
       <c r="K42" s="3">
         <v>4900</v>
@@ -3912,8 +3911,8 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>16</v>
+      <c r="D43" s="3">
+        <v>700</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>16</v>
@@ -3921,11 +3920,11 @@
       <c r="F43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="3">
         <v>500</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>16</v>
@@ -4025,8 +4024,8 @@
       <c r="F44" s="3">
         <v>0</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>16</v>
+      <c r="G44" s="3">
+        <v>0</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>16</v>
@@ -4120,8 +4119,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>16</v>
+      <c r="D45" s="3">
+        <v>9300</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>16</v>
@@ -4129,17 +4128,17 @@
       <c r="F45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="3">
         <v>4600</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="3">
         <v>300</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="K45" s="3">
         <v>2800</v>
@@ -4228,22 +4227,22 @@
         <v>40100</v>
       </c>
       <c r="E46" s="3">
+        <v>36700</v>
+      </c>
+      <c r="F46" s="3">
         <v>31500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>29800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>28600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>26900</v>
-      </c>
-      <c r="J46" s="3">
-        <v>27000</v>
       </c>
       <c r="K46" s="3">
         <v>26600</v>
@@ -4436,16 +4435,16 @@
         <v>3300</v>
       </c>
       <c r="E48" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F48" s="3">
         <v>1600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>900</v>
-      </c>
-      <c r="H48" s="3">
-        <v>700</v>
       </c>
       <c r="I48" s="3">
         <v>700</v>
@@ -4555,7 +4554,7 @@
         <v>100</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K49" s="3">
         <v>100</v>
@@ -4852,22 +4851,22 @@
         <v>500</v>
       </c>
       <c r="E52" s="3">
+        <v>400</v>
+      </c>
+      <c r="F52" s="3">
         <v>300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>200</v>
       </c>
       <c r="K52" s="3">
         <v>200</v>
@@ -5060,22 +5059,22 @@
         <v>43900</v>
       </c>
       <c r="E54" s="3">
+        <v>38900</v>
+      </c>
+      <c r="F54" s="3">
         <v>33500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>29800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27900</v>
-      </c>
-      <c r="J54" s="3">
-        <v>28000</v>
       </c>
       <c r="K54" s="3">
         <v>27600</v>
@@ -5347,19 +5346,19 @@
         <v>800</v>
       </c>
       <c r="F58" s="3">
+        <v>800</v>
+      </c>
+      <c r="G58" s="3">
         <v>500</v>
-      </c>
-      <c r="G58" s="3">
-        <v>600</v>
       </c>
       <c r="H58" s="3">
         <v>600</v>
       </c>
       <c r="I58" s="3">
+        <v>600</v>
+      </c>
+      <c r="J58" s="3">
         <v>500</v>
-      </c>
-      <c r="J58" s="3">
-        <v>400</v>
       </c>
       <c r="K58" s="3">
         <v>400</v>
@@ -5445,25 +5444,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>49000</v>
+        <v>49400</v>
       </c>
       <c r="E59" s="3">
+        <v>43600</v>
+      </c>
+      <c r="F59" s="3">
         <v>38900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>34500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>32600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>18600</v>
       </c>
       <c r="K59" s="3">
         <v>15800</v>
@@ -5552,22 +5551,22 @@
         <v>56900</v>
       </c>
       <c r="E60" s="3">
+        <v>51600</v>
+      </c>
+      <c r="F60" s="3">
         <v>46000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>42500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>39100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26400</v>
-      </c>
-      <c r="J60" s="3">
-        <v>23000</v>
       </c>
       <c r="K60" s="3">
         <v>20500</v>
@@ -5656,11 +5655,11 @@
         <v>1400</v>
       </c>
       <c r="E61" s="3">
+        <v>400</v>
+      </c>
+      <c r="F61" s="3">
         <v>500</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -5668,10 +5667,10 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>100</v>
-      </c>
-      <c r="J61" s="3">
-        <v>200</v>
       </c>
       <c r="K61" s="3">
         <v>300</v>
@@ -5756,8 +5755,8 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>300</v>
+      <c r="D62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>16</v>
@@ -6176,22 +6175,22 @@
         <v>58700</v>
       </c>
       <c r="E66" s="3">
+        <v>52300</v>
+      </c>
+      <c r="F66" s="3">
         <v>46800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>42800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>39300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26700</v>
-      </c>
-      <c r="J66" s="3">
-        <v>23500</v>
       </c>
       <c r="K66" s="3">
         <v>21100</v>
@@ -6730,8 +6729,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>16</v>
+      <c r="D72" s="3">
+        <v>-353600</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>16</v>
@@ -6739,11 +6738,11 @@
       <c r="F72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H72" s="3">
         <v>-346400</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>16</v>
@@ -7150,22 +7149,22 @@
         <v>-15000</v>
       </c>
       <c r="E76" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="F76" s="3">
         <v>-13600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-12300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-8300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-2600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1200</v>
-      </c>
-      <c r="J76" s="3">
-        <v>4500</v>
       </c>
       <c r="K76" s="3">
         <v>6600</v>
@@ -7363,22 +7362,22 @@
         <v>45657</v>
       </c>
       <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
-      </c>
-      <c r="J80" s="2">
-        <v>45016</v>
       </c>
       <c r="K80" s="2">
         <v>44926</v>
@@ -7467,22 +7466,22 @@
         <v>-1600</v>
       </c>
       <c r="E81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2900</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-2400</v>
       </c>
       <c r="K81" s="3">
         <v>-2000</v>

--- a/AAII_Financials/Quarterly/COE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/COE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="92">
   <si>
     <t>COE</t>
   </si>
@@ -656,466 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3">
         <v>16200</v>
       </c>
-      <c r="E8" s="3">
-        <v>14000</v>
-      </c>
-      <c r="F8" s="3">
-        <v>11000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>9400</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3">
         <v>7500</v>
       </c>
-      <c r="I8" s="3">
-        <v>7800</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="3">
         <v>6300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2181500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>573600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>579800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>92400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>535100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>538500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>72700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>76800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>62000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>62900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>53900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>48700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>43300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>44000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>39400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>37700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>38700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>35000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>28500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>23200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>18600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3">
         <v>3700</v>
       </c>
-      <c r="E9" s="3">
-        <v>3000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1900</v>
+      <c r="F9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I9" s="3">
         <v>1900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="3">
         <v>1400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>558000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>151900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>158100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>24600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>146100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>146700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>21200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>22700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>17500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>17900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>16400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>16200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>15900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>13300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>14500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>13400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>10600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>8000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="3">
         <v>12600</v>
       </c>
-      <c r="E10" s="3">
-        <v>11100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>8600</v>
-      </c>
-      <c r="G10" s="3">
-        <v>7300</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="3">
         <v>5600</v>
       </c>
-      <c r="I10" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="3">
         <v>4900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1623500</v>
-      </c>
-      <c r="P10" s="3">
-        <v>421700</v>
       </c>
       <c r="Q10" s="3">
         <v>421700</v>
       </c>
       <c r="R10" s="3">
+        <v>421700</v>
+      </c>
+      <c r="S10" s="3">
         <v>67800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>389000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>391800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>51600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>54100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>44500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>45100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>37400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>32600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>27100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>28100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>25900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>24300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>24100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>21700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>17900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>15200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>12000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1152,112 +1165,116 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="3">
         <v>900</v>
       </c>
-      <c r="E12" s="3">
-        <v>800</v>
-      </c>
-      <c r="F12" s="3">
-        <v>900</v>
-      </c>
-      <c r="G12" s="3">
-        <v>900</v>
-      </c>
-      <c r="H12" s="3">
-        <v>900</v>
+      <c r="F12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I12" s="3">
         <v>900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>178800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>40700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>65000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>8900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>44600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>43800</v>
-      </c>
-      <c r="U12" s="3">
-        <v>5700</v>
       </c>
       <c r="V12" s="3">
         <v>5700</v>
       </c>
       <c r="W12" s="3">
+        <v>5700</v>
+      </c>
+      <c r="X12" s="3">
         <v>5800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>6300</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>6200</v>
       </c>
       <c r="AA12" s="3">
         <v>6200</v>
       </c>
       <c r="AB12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="AC12" s="3">
         <v>6600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>6200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>7500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>9000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>9100</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>7500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>7400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>6700</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1360,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1395,51 +1415,51 @@
       <c r="M14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>21500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>31800</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-7400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-7600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-1000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-1600</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>16</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>1100</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>16</v>
       </c>
@@ -1455,8 +1475,8 @@
       <c r="AG14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1464,8 +1484,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1568,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1603,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="3">
         <v>17100</v>
       </c>
-      <c r="E17" s="3">
-        <v>14800</v>
-      </c>
-      <c r="F17" s="3">
-        <v>13400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>13400</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="F17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="3">
         <v>11800</v>
       </c>
-      <c r="I17" s="3">
-        <v>11700</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="3">
         <v>9200</v>
-      </c>
-      <c r="K17" s="3">
-        <v>7200</v>
       </c>
       <c r="L17" s="3">
         <v>7200</v>
       </c>
       <c r="M17" s="3">
+        <v>7200</v>
+      </c>
+      <c r="N17" s="3">
         <v>7600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2132200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>515200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>613600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>91500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>524100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>517100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>68700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>69800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>63000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>64000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>59200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>58400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>63100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>56900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>50100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>53500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>61400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>55800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>48900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>43600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>40600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="3">
         <v>-900</v>
       </c>
-      <c r="E18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="F18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="3">
         <v>-4300</v>
       </c>
-      <c r="I18" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="3">
         <v>-3000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>49300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>58400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-33800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>21400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7100</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-1000</v>
       </c>
       <c r="X18" s="3">
         <v>-1000</v>
       </c>
       <c r="Y18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-19800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-12900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-10700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-15900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-22700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-20700</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>-20400</v>
       </c>
       <c r="AH18" s="3">
         <v>-20400</v>
       </c>
       <c r="AI18" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>-21900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1849,142 +1882,146 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="M20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O20" s="3">
+        <v>100</v>
+      </c>
+      <c r="P20" s="3">
+        <v>25100</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="R20" s="3">
+        <v>9600</v>
+      </c>
+      <c r="S20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T20" s="3">
+        <v>11900</v>
+      </c>
+      <c r="U20" s="3">
+        <v>11700</v>
+      </c>
+      <c r="V20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X20" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="AD20" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="AI20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>25100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>9600</v>
-      </c>
-      <c r="R20" s="3">
-        <v>1300</v>
-      </c>
-      <c r="S20" s="3">
-        <v>11900</v>
-      </c>
-      <c r="T20" s="3">
-        <v>11700</v>
-      </c>
-      <c r="U20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="V20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="W20" s="3">
-        <v>600</v>
-      </c>
-      <c r="X20" s="3">
-        <v>400</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>500</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AJ20" s="3">
         <v>-400</v>
       </c>
-      <c r="AB20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>500</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AH20" s="3">
+      <c r="AK20" s="3">
         <v>100</v>
       </c>
-      <c r="AI20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>100</v>
-      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1500</v>
       </c>
-      <c r="E21" s="3">
-        <v>-600</v>
-      </c>
       <c r="F21" s="3">
-        <v>-1300</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>-3800</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>-5500</v>
       </c>
-      <c r="I21" s="3">
-        <v>-3900</v>
-      </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>-3000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>16</v>
       </c>
@@ -2057,8 +2094,11 @@
       <c r="AJ21" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2092,11 +2132,11 @@
       <c r="M22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>16</v>
+      <c r="N22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>16</v>
@@ -2104,17 +2144,17 @@
       <c r="Q22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>16</v>
+      <c r="R22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -2161,139 +2201,145 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1500</v>
       </c>
-      <c r="E23" s="3">
-        <v>-600</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="3">
         <v>-5500</v>
       </c>
-      <c r="I23" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" s="3">
         <v>-3000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>74400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>52200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-24100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>22900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>33200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>8200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-9900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-20200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-13000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-10200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-23500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-20900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-20500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-20300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-22400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-17900</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
-        <v>100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -2304,28 +2350,28 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-46100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-20500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-8900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
-      </c>
-      <c r="V24" s="3">
-        <v>200</v>
       </c>
       <c r="W24" s="3">
         <v>200</v>
@@ -2340,7 +2386,7 @@
         <v>200</v>
       </c>
       <c r="AA24" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AB24" s="3">
         <v>100</v>
@@ -2349,19 +2395,19 @@
         <v>100</v>
       </c>
       <c r="AD24" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE24" s="3">
         <v>200</v>
       </c>
       <c r="AF24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>200</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>100</v>
       </c>
       <c r="AI24" s="3">
         <v>100</v>
@@ -2369,8 +2415,11 @@
       <c r="AJ24" s="3">
         <v>100</v>
       </c>
+      <c r="AK24" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2473,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1700</v>
       </c>
-      <c r="E26" s="3">
-        <v>-700</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="3">
         <v>-5700</v>
       </c>
-      <c r="I26" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>120600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>72700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-27000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>31800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>31600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-13100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-10300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-16200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-23700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-21000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-20700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-20400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-22400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
-        <v>-600</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="3">
         <v>-5700</v>
       </c>
-      <c r="I27" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>120600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>72700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-27000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>31800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>31600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-13100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-10300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-16200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-23700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-21000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-20700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-20400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-22400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2785,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2818,14 +2879,14 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-10400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-17700</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P29" s="3" t="s">
         <v>16</v>
       </c>
@@ -2838,8 +2899,8 @@
       <c r="S29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2859,14 +2920,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>16</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -2889,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2993,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3097,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="M32" s="3">
+        <v>200</v>
+      </c>
+      <c r="N32" s="3">
+        <v>500</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>6200</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="AD32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>800</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>500</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="AI32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>-25100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>6200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-9600</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-11900</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-11700</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>200</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AJ32" s="3">
         <v>400</v>
       </c>
-      <c r="AB32" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>200</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>800</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>200</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>100</v>
-      </c>
-      <c r="AH32" s="3">
+      <c r="AK32" s="3">
         <v>-100</v>
       </c>
-      <c r="AI32" s="3">
-        <v>400</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>-100</v>
-      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1600</v>
       </c>
-      <c r="E33" s="3">
-        <v>-600</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="3">
         <v>-5700</v>
       </c>
-      <c r="I33" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33" s="3">
         <v>-2900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-21200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>120600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>72700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-27000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>31800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>31600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>8000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-13100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-10300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-16200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-23700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-21000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-20700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-20400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-22400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3409,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1600</v>
       </c>
-      <c r="E35" s="3">
-        <v>-600</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="3">
         <v>-5700</v>
       </c>
-      <c r="I35" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K35" s="3">
         <v>-2900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-21200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>120600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>72700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-27000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>31800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>31600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>8000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-13100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-10300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-16200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-23700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-21000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-20700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-20400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-22400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3660,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3698,205 +3784,209 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="3">
         <v>27800</v>
       </c>
-      <c r="E41" s="3">
-        <v>22200</v>
-      </c>
-      <c r="F41" s="3">
-        <v>16700</v>
-      </c>
-      <c r="G41" s="3">
-        <v>17400</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="3">
         <v>21300</v>
       </c>
-      <c r="I41" s="3">
-        <v>20000</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K41" s="3">
         <v>16900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>21100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>54900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>41300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>624900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>842900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>769300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>804100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>595900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>79200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>85800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>76800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>68000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>67600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>67100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>83600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>85900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>77100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>74400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>77600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>85900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>104100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>96500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>94100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>90500</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>1400</v>
       </c>
-      <c r="E42" s="3">
-        <v>3400</v>
-      </c>
       <c r="F42" s="3">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>2100</v>
       </c>
-      <c r="I42" s="3">
-        <v>2900</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>4800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4900</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N42" s="3">
+      <c r="N42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O42" s="3">
         <v>48000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>90700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>610800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>387900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>449000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>509600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>441900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>65100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>71400</v>
-      </c>
-      <c r="W42" s="3">
-        <v>71500</v>
       </c>
       <c r="X42" s="3">
         <v>71500</v>
       </c>
       <c r="Y42" s="3">
+        <v>71500</v>
+      </c>
+      <c r="Z42" s="3">
         <v>52500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>39000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>19800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>9500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>7100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>4300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>14900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>11600</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AH42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3906,40 +3996,43 @@
       <c r="AJ42" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="3">
         <v>500</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>16</v>
+      <c r="L43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>16</v>
@@ -3950,8 +4043,8 @@
       <c r="P43" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4010,22 +4103,25 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
+      <c r="E44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>16</v>
@@ -4045,48 +4141,48 @@
       <c r="M44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N44" s="3">
-        <v>200</v>
+      <c r="N44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O44" s="3">
         <v>200</v>
       </c>
       <c r="P44" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q44" s="3">
         <v>1700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1600</v>
-      </c>
-      <c r="U44" s="3">
-        <v>100</v>
       </c>
       <c r="V44" s="3">
         <v>100</v>
       </c>
       <c r="W44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
         <v>100</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
-      </c>
       <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
         <v>100</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB44" s="3" t="s">
         <v>16</v>
       </c>
@@ -4096,8 +4192,8 @@
       <c r="AD44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AE44" s="3">
-        <v>0</v>
+      <c r="AE44" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AF44" s="3">
         <v>0</v>
@@ -4114,216 +4210,225 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="3">
         <v>9300</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="3">
         <v>4600</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K45" s="3">
         <v>300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>22500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>19200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>295300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>327500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>314700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>302100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>292100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>39500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>39100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>39500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>39600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>40300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>39500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>35200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>34100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>28300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>24900</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>12600</v>
       </c>
       <c r="AF45" s="3">
         <v>12600</v>
       </c>
       <c r="AG45" s="3">
+        <v>12600</v>
+      </c>
+      <c r="AH45" s="3">
         <v>9700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>10900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="3">
         <v>40100</v>
       </c>
-      <c r="E46" s="3">
-        <v>36700</v>
-      </c>
-      <c r="F46" s="3">
-        <v>31500</v>
-      </c>
-      <c r="G46" s="3">
-        <v>29600</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="3">
         <v>29800</v>
       </c>
-      <c r="I46" s="3">
-        <v>28600</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K46" s="3">
         <v>26900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>26600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>26100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>125500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>151300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1532700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1560200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1534000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1617700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1331400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>184000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>196500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>187800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>179300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>160400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>145600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>138600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>129600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>112400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>103700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>105100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>110000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>113900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>107400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>103700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>98200</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4351,8 +4456,8 @@
       <c r="K47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4426,135 +4531,141 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="3">
         <v>3300</v>
       </c>
-      <c r="E48" s="3">
-        <v>1700</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="3">
+        <v>900</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K48" s="3">
+        <v>700</v>
+      </c>
+      <c r="L48" s="3">
         <v>800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="M48" s="3">
         <v>900</v>
       </c>
-      <c r="I48" s="3">
-        <v>700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>700</v>
-      </c>
-      <c r="K48" s="3">
-        <v>800</v>
-      </c>
-      <c r="L48" s="3">
-        <v>900</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>86300</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>144000</v>
       </c>
       <c r="R48" s="3">
         <v>144000</v>
       </c>
       <c r="S48" s="3">
+        <v>144000</v>
+      </c>
+      <c r="T48" s="3">
         <v>119200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>89300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13900</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>11600</v>
       </c>
       <c r="Z48" s="3">
         <v>11600</v>
       </c>
       <c r="AA48" s="3">
+        <v>11600</v>
+      </c>
+      <c r="AB48" s="3">
         <v>5100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>100</v>
+      <c r="D49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E49" s="3">
         <v>100</v>
       </c>
-      <c r="F49" s="3">
-        <v>100</v>
-      </c>
-      <c r="G49" s="3">
-        <v>100</v>
-      </c>
-      <c r="H49" s="3">
-        <v>100</v>
+      <c r="F49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I49" s="3">
         <v>100</v>
       </c>
-      <c r="J49" s="3">
-        <v>100</v>
+      <c r="J49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K49" s="3">
         <v>100</v>
@@ -4566,43 +4677,43 @@
         <v>100</v>
       </c>
       <c r="N49" s="3">
+        <v>100</v>
+      </c>
+      <c r="O49" s="3">
         <v>1600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>44900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>23000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>24500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>12300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2100</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>2300</v>
       </c>
       <c r="AA49" s="3">
         <v>2300</v>
@@ -4611,31 +4722,34 @@
         <v>2300</v>
       </c>
       <c r="AC49" s="3">
-        <v>1900</v>
+        <v>2300</v>
       </c>
       <c r="AD49" s="3">
         <v>1900</v>
       </c>
       <c r="AE49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AF49" s="3">
         <v>2100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4738,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4842,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="3">
         <v>500</v>
       </c>
-      <c r="E52" s="3">
-        <v>400</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" s="3">
         <v>300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K52" s="3">
+        <v>300</v>
+      </c>
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="M52" s="3">
         <v>300</v>
       </c>
-      <c r="I52" s="3">
-        <v>400</v>
-      </c>
-      <c r="J52" s="3">
-        <v>300</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3">
-        <v>300</v>
-      </c>
-      <c r="M52" s="3">
-        <v>200</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>23700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>71300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>447000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>543600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>448200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>573500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>67400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>35600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>19000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1800</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>1700</v>
       </c>
       <c r="AD52" s="3">
         <v>1700</v>
       </c>
       <c r="AE52" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="AF52" s="3">
         <v>1800</v>
       </c>
       <c r="AG52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AH52" s="3">
         <v>2100</v>
-      </c>
-      <c r="AH52" s="3">
-        <v>1800</v>
       </c>
       <c r="AI52" s="3">
         <v>1800</v>
       </c>
       <c r="AJ52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AK52" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5050,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="3">
         <v>43900</v>
       </c>
-      <c r="E54" s="3">
-        <v>38900</v>
-      </c>
-      <c r="F54" s="3">
-        <v>33500</v>
-      </c>
-      <c r="G54" s="3">
-        <v>30800</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" s="3">
         <v>31200</v>
       </c>
-      <c r="I54" s="3">
-        <v>29800</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K54" s="3">
         <v>27900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>157400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>187100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1702400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2196100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2244500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2209500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2006600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>265300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>246900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>221200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>196300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>175300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>160400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>146700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>138700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>121500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>113800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>116300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>121100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>123300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>116300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>112800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>105500</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5192,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5230,8 +5360,9 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5259,8 +5390,8 @@
       <c r="K57" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -5334,38 +5465,41 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="3">
         <v>1200</v>
       </c>
-      <c r="E58" s="3">
-        <v>800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>500</v>
-      </c>
-      <c r="H58" s="3">
-        <v>600</v>
+      <c r="F58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="I58" s="3">
         <v>600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="J58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5397,32 +5531,32 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>2600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>8300</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD58" s="3">
         <v>3500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>800</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>16</v>
       </c>
@@ -5438,227 +5572,236 @@
       <c r="AJ58" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="3">
         <v>49400</v>
       </c>
-      <c r="E59" s="3">
-        <v>43600</v>
-      </c>
-      <c r="F59" s="3">
-        <v>38900</v>
-      </c>
-      <c r="G59" s="3">
-        <v>34500</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="3">
         <v>32600</v>
       </c>
-      <c r="I59" s="3">
-        <v>26300</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K59" s="3">
         <v>21200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>291100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2047300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2452600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3000500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3050200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3018100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2842300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>392700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>396400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>378900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>346200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>324900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>304100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>273800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>245200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>221500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>210900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>211400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>192100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>172400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>143000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>122000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>97500</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="3">
         <v>56900</v>
       </c>
-      <c r="E60" s="3">
-        <v>51600</v>
-      </c>
-      <c r="F60" s="3">
-        <v>46000</v>
-      </c>
-      <c r="G60" s="3">
-        <v>42500</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" s="3">
         <v>39100</v>
       </c>
-      <c r="I60" s="3">
-        <v>32200</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K60" s="3">
         <v>26400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>20500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>291100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>297000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2452600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3000500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3050200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3018100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2842300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>392700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>396400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>381600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>350800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>331400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>312500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>273800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>245200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>225000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>211700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>211400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>192100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>172400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>143000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>122000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>97500</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>1400</v>
       </c>
-      <c r="E61" s="3">
-        <v>400</v>
-      </c>
       <c r="F61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -5670,14 +5813,14 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5721,14 +5864,14 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>10000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11100</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5750,8 +5893,11 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5779,83 +5925,86 @@
       <c r="K62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M62" s="3">
         <v>600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>38100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>62200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>62700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>58400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>33700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5958,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6062,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6166,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="3">
         <v>58700</v>
       </c>
-      <c r="E66" s="3">
-        <v>52300</v>
-      </c>
-      <c r="F66" s="3">
-        <v>46800</v>
-      </c>
-      <c r="G66" s="3">
-        <v>42800</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" s="3">
         <v>39300</v>
       </c>
-      <c r="I66" s="3">
-        <v>32400</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K66" s="3">
         <v>26700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>21100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>294100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>300500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2490600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3062700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3112900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3076500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2876000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>397400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>401500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>386300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>356500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>335300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>316700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>286500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>260000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>228000</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>215500</v>
       </c>
       <c r="AE66" s="3">
         <v>215500</v>
       </c>
       <c r="AF66" s="3">
+        <v>215500</v>
+      </c>
+      <c r="AG66" s="3">
         <v>197000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>178400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>150100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>127200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>101800</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6308,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6412,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6516,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6620,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6724,50 +6895,53 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="3">
         <v>-353600</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" s="3">
         <v>-346400</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L72" s="3">
         <v>-331200</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P72" s="3">
         <v>-1931400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6783,8 +6957,8 @@
       <c r="U72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
+      <c r="V72" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W72" s="3">
         <v>0</v>
@@ -6804,32 +6978,35 @@
       <c r="AB72" s="3">
         <v>0</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>16</v>
+      <c r="AC72" s="3">
+        <v>0</v>
       </c>
       <c r="AD72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF72" s="3">
         <v>-260300</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AH72" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>-170600</v>
       </c>
-      <c r="AJ72" s="3" t="s">
+      <c r="AK72" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6932,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7036,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7140,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="3">
         <v>-15000</v>
       </c>
-      <c r="E76" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="F76" s="3">
-        <v>-13600</v>
-      </c>
-      <c r="G76" s="3">
-        <v>-12300</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="3">
         <v>-8300</v>
       </c>
-      <c r="I76" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K76" s="3">
         <v>1200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-136700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-113400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-788200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-866600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-868300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-866900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-869400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-132000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-154700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-165100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-160200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-160000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-156300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-139800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-121200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-106500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-101700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-99200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-75900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-55000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-33700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-14400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7348,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1600</v>
       </c>
-      <c r="E81" s="3">
-        <v>-600</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" s="3">
         <v>-5700</v>
       </c>
-      <c r="I81" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K81" s="3">
         <v>-2900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-21200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>120600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>72700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-27000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>31800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>31600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>8000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-10100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-13100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-10300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-16200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-23700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-21000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-20700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-20400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-22400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-18000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7599,8 +7797,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7628,8 +7827,8 @@
       <c r="K83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -7703,8 +7902,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7807,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7911,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8015,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8119,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8223,8 +8437,11 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8252,8 +8469,8 @@
       <c r="K89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -8327,8 +8544,11 @@
       <c r="AJ89" s="3">
         <v>0</v>
       </c>
+      <c r="AK89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8365,8 +8585,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8394,8 +8615,8 @@
       <c r="K91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8469,8 +8690,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8573,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8677,8 +8904,11 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8706,8 +8936,8 @@
       <c r="K94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -8781,8 +9011,11 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8819,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8848,8 +9082,8 @@
       <c r="K96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8923,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9027,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9131,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9235,8 +9478,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9264,8 +9510,8 @@
       <c r="K100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -9339,8 +9585,11 @@
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9368,8 +9617,8 @@
       <c r="K101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9443,8 +9692,11 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9472,8 +9724,8 @@
       <c r="K102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -9545,6 +9797,9 @@
         <v>0</v>
       </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>0</v>
       </c>
     </row>
